--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC3B40B-B2FC-4C5C-AF19-E6DD7287BF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D46A6EB-B58F-4C19-93FB-DD94DE2B1921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15324" windowHeight="12336" tabRatio="868" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -24,29 +24,30 @@
     <sheet name="Nazionalità | Nationalitäten" sheetId="9" r:id="rId9"/>
     <sheet name="Colori | Farben" sheetId="10" r:id="rId10"/>
     <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId11"/>
-    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId12"/>
-    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId13"/>
-    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId14"/>
-    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId15"/>
-    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId16"/>
-    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId17"/>
-    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId18"/>
-    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId19"/>
-    <sheet name="Animali | Tiere" sheetId="21" r:id="rId20"/>
-    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId21"/>
-    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId22"/>
-    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId23"/>
-    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId24"/>
-    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId25"/>
-    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId26"/>
-    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId27"/>
+    <sheet name="Meine Worte" sheetId="29" r:id="rId12"/>
+    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId13"/>
+    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId14"/>
+    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId15"/>
+    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId16"/>
+    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId17"/>
+    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId18"/>
+    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId19"/>
+    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId20"/>
+    <sheet name="Animali | Tiere" sheetId="21" r:id="rId21"/>
+    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId22"/>
+    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId23"/>
+    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId24"/>
+    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId25"/>
+    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId26"/>
+    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId27"/>
+    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId28"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2584" uniqueCount="1862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2629" uniqueCount="1884">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -5714,6 +5715,72 @@
   </si>
   <si>
     <t>Ich wohne in …</t>
+  </si>
+  <si>
+    <t>Vocabolario</t>
+  </si>
+  <si>
+    <t>e poi</t>
+  </si>
+  <si>
+    <t>la mattina</t>
+  </si>
+  <si>
+    <t>il pomerigo</t>
+  </si>
+  <si>
+    <t>doccia</t>
+  </si>
+  <si>
+    <t>di solita</t>
+  </si>
+  <si>
+    <t>posso</t>
+  </si>
+  <si>
+    <t>lontano</t>
+  </si>
+  <si>
+    <t>und dann</t>
+  </si>
+  <si>
+    <t>der Morgen / am Morgen</t>
+  </si>
+  <si>
+    <t>die Dusche</t>
+  </si>
+  <si>
+    <t>ich kann</t>
+  </si>
+  <si>
+    <t>weit/fern</t>
+  </si>
+  <si>
+    <t>infine</t>
+  </si>
+  <si>
+    <t>schließlich</t>
+  </si>
+  <si>
+    <t>allora</t>
+  </si>
+  <si>
+    <t>dann/also</t>
+  </si>
+  <si>
+    <t>voglio</t>
+  </si>
+  <si>
+    <t>ich will</t>
+  </si>
+  <si>
+    <t>vicino</t>
+  </si>
+  <si>
+    <t>nah</t>
+  </si>
+  <si>
+    <t>fern/weit</t>
   </si>
 </sst>
 </file>
@@ -6982,6 +7049,224 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B66C6F-8A66-46FF-A81A-50D89DD6569D}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7616,7 +7901,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7966,7 +8251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8316,7 +8601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8761,7 +9046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9187,7 +9472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9537,7 +9822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9876,261 +10161,6 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1375</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1376</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1377</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1379</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1380</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1384</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1387</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1391</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1392</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1394</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1395</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1396</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1397</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1398</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1400</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1401</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1403</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1404</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1405</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1406</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1407</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1408</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1410</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1411</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1412</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1415</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1416</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10872,6 +10902,261 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1384</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1392</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11411,7 +11696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11761,7 +12046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -11959,7 +12244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12176,7 +12461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12526,7 +12811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12819,7 +13104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -13248,7 +13533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D46A6EB-B58F-4C19-93FB-DD94DE2B1921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C203CF79-F9F2-48D9-8013-15436C6614E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="15324" windowHeight="12336" tabRatio="868" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -25,29 +25,31 @@
     <sheet name="Colori | Farben" sheetId="10" r:id="rId10"/>
     <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId11"/>
     <sheet name="Meine Worte" sheetId="29" r:id="rId12"/>
-    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId13"/>
-    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId14"/>
-    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId15"/>
-    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId16"/>
-    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId17"/>
-    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId18"/>
-    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId19"/>
-    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId20"/>
-    <sheet name="Animali | Tiere" sheetId="21" r:id="rId21"/>
-    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId22"/>
-    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId23"/>
-    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId24"/>
-    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId25"/>
-    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId26"/>
-    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId27"/>
-    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId28"/>
+    <sheet name="Wegbeschreibung" sheetId="31" r:id="rId13"/>
+    <sheet name="Traffico | Verkehr" sheetId="30" r:id="rId14"/>
+    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId15"/>
+    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId16"/>
+    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId17"/>
+    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId18"/>
+    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId19"/>
+    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId20"/>
+    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId21"/>
+    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId22"/>
+    <sheet name="Animali | Tiere" sheetId="21" r:id="rId23"/>
+    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId24"/>
+    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId25"/>
+    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId26"/>
+    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId27"/>
+    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId28"/>
+    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId29"/>
+    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId30"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2629" uniqueCount="1884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1982">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -5781,6 +5783,300 @@
   </si>
   <si>
     <t>fern/weit</t>
+  </si>
+  <si>
+    <t>purtroppo</t>
+  </si>
+  <si>
+    <t>Potresti</t>
+  </si>
+  <si>
+    <t>leider</t>
+  </si>
+  <si>
+    <t>andare dritto</t>
+  </si>
+  <si>
+    <t>geradeaus gehen</t>
+  </si>
+  <si>
+    <t>Verkehr</t>
+  </si>
+  <si>
+    <t>girare a sinstra</t>
+  </si>
+  <si>
+    <t>links abbiegen</t>
+  </si>
+  <si>
+    <t>girare a destra</t>
+  </si>
+  <si>
+    <t>rechts abbiegen</t>
+  </si>
+  <si>
+    <t>tornare indietro</t>
+  </si>
+  <si>
+    <t>zurückgehen/umkehren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attraversare la strada </t>
+  </si>
+  <si>
+    <t>die Straße überqueren</t>
+  </si>
+  <si>
+    <t>prendere la seconda traversa a destra</t>
+  </si>
+  <si>
+    <t>die zweite Straße rechts nehmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arrivare al semaforo </t>
+  </si>
+  <si>
+    <t>zur Ampel kommen</t>
+  </si>
+  <si>
+    <t>superare l´icrocio</t>
+  </si>
+  <si>
+    <t>die Kreuzung überqueren</t>
+  </si>
+  <si>
+    <t>il semaforo</t>
+  </si>
+  <si>
+    <t>Ampel</t>
+  </si>
+  <si>
+    <t>l'incrocio</t>
+  </si>
+  <si>
+    <t>Kreuzung</t>
+  </si>
+  <si>
+    <t>lo spartitraffico</t>
+  </si>
+  <si>
+    <t>Mittelstreifen</t>
+  </si>
+  <si>
+    <t>la strada</t>
+  </si>
+  <si>
+    <t>Straße</t>
+  </si>
+  <si>
+    <t>il traffico</t>
+  </si>
+  <si>
+    <t>l'ingorgo</t>
+  </si>
+  <si>
+    <t>Stau</t>
+  </si>
+  <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>Fahrrad</t>
+  </si>
+  <si>
+    <t>il pedone</t>
+  </si>
+  <si>
+    <t>Fußgänger</t>
+  </si>
+  <si>
+    <t>fermarsi al semaforo</t>
+  </si>
+  <si>
+    <t>an der Ampel anhalten</t>
+  </si>
+  <si>
+    <t>parcheggiare la macchina</t>
+  </si>
+  <si>
+    <t>das Auto parken</t>
+  </si>
+  <si>
+    <t>attraversare sulle strisce</t>
+  </si>
+  <si>
+    <t>auf dem Zebrastreifen überqueren</t>
+  </si>
+  <si>
+    <t>il marciapiede</t>
+  </si>
+  <si>
+    <t>der Bürgersteig</t>
+  </si>
+  <si>
+    <t>le strisce pedonali</t>
+  </si>
+  <si>
+    <t>der Zebrastreifen</t>
+  </si>
+  <si>
+    <t>il limite di velocità</t>
+  </si>
+  <si>
+    <t>das Tempolimit</t>
+  </si>
+  <si>
+    <t>la multa</t>
+  </si>
+  <si>
+    <t>der Strafzettel</t>
+  </si>
+  <si>
+    <t>il parcheggio</t>
+  </si>
+  <si>
+    <t>der Parkplatz</t>
+  </si>
+  <si>
+    <t>la rotonda</t>
+  </si>
+  <si>
+    <t>der Kreisverkehr</t>
+  </si>
+  <si>
+    <t>il vigile</t>
+  </si>
+  <si>
+    <t>der Verkehrspolizist</t>
+  </si>
+  <si>
+    <t>la patente</t>
+  </si>
+  <si>
+    <t>der Führerschein</t>
+  </si>
+  <si>
+    <t>la cintura di sicurezza</t>
+  </si>
+  <si>
+    <t>der Sicherheitsgurt</t>
+  </si>
+  <si>
+    <t>La chiesa è fra il museo e il teatro.</t>
+  </si>
+  <si>
+    <t>Die Kirche ist zwischen dem Museum und dem Theater.</t>
+  </si>
+  <si>
+    <t>L'ufficio postale è accanto alla banca.</t>
+  </si>
+  <si>
+    <t>Das Postamt ist neben der Bank.</t>
+  </si>
+  <si>
+    <t>Il distributore è dietro la stazione.</t>
+  </si>
+  <si>
+    <t>Die Tankstelle ist hinter dem Bahnhof.</t>
+  </si>
+  <si>
+    <t>Il parcheggio è davanti alla scuola.</t>
+  </si>
+  <si>
+    <t>Der Parkplatz ist vor der Schule.</t>
+  </si>
+  <si>
+    <t>Il bar è all'angolo.</t>
+  </si>
+  <si>
+    <t>Die Bar ist an der Ecke.</t>
+  </si>
+  <si>
+    <t>La fermata dell'autobus è di fronte al supermercato.</t>
+  </si>
+  <si>
+    <t>Die Bushaltestelle ist gegenüber dem Supermarkt.</t>
+  </si>
+  <si>
+    <t>La chiesa</t>
+  </si>
+  <si>
+    <t>L'ufficio postale</t>
+  </si>
+  <si>
+    <t>das Postamt</t>
+  </si>
+  <si>
+    <t>Il distributore</t>
+  </si>
+  <si>
+    <t>die Tankstelle</t>
+  </si>
+  <si>
+    <t>Il parcheggio</t>
+  </si>
+  <si>
+    <t>Il bar</t>
+  </si>
+  <si>
+    <t>La fermata dell'autobus</t>
+  </si>
+  <si>
+    <t>die Bushaltestelle</t>
+  </si>
+  <si>
+    <t>La banca</t>
+  </si>
+  <si>
+    <t>Il supermercato</t>
+  </si>
+  <si>
+    <t>La scuola</t>
+  </si>
+  <si>
+    <t>La stazione</t>
+  </si>
+  <si>
+    <t>Il museo</t>
+  </si>
+  <si>
+    <t>Il teatro</t>
+  </si>
+  <si>
+    <t>L'angolo</t>
+  </si>
+  <si>
+    <t>die Ecke</t>
+  </si>
+  <si>
+    <t>davanti a</t>
+  </si>
+  <si>
+    <t>vor</t>
+  </si>
+  <si>
+    <t>dietro</t>
+  </si>
+  <si>
+    <t>hinter</t>
+  </si>
+  <si>
+    <t>accanto a</t>
+  </si>
+  <si>
+    <t>neben</t>
+  </si>
+  <si>
+    <t>di fronte a</t>
+  </si>
+  <si>
+    <t>gegenüber</t>
+  </si>
+  <si>
+    <t>fra / tra</t>
+  </si>
+  <si>
+    <t>zwischen</t>
   </si>
 </sst>
 </file>
@@ -5901,9 +6197,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -6224,6 +6520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Tabelle1"/>
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -6234,6 +6531,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr codeName="Tabelle10"/>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6243,26 +6541,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>736</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -6660,7 +6958,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Tabelle11">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:G40"/>
@@ -6672,26 +6970,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>813</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7050,36 +7348,36 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B66C6F-8A66-46FF-A81A-50D89DD6569D}">
-  <sheetPr>
+  <sheetPr codeName="Tabelle12">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7255,6 +7553,19 @@
       </c>
       <c r="B21" t="s">
         <v>1883</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1885</v>
       </c>
     </row>
   </sheetData>
@@ -7267,7 +7578,653 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E588DC5B-33F8-491D-A40A-9A11B571492D}">
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B21" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0357D6F-E5C9-4C7A-8B99-03AFE50AD46D}">
+  <sheetPr codeName="Tabelle29"/>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="7" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr codeName="Tabelle13"/>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7277,26 +8234,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>853</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7890,706 +8847,6 @@
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>975</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D4" t="s">
-        <v>979</v>
-      </c>
-      <c r="E4" t="s">
-        <v>980</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D5" t="s">
-        <v>983</v>
-      </c>
-      <c r="E5" t="s">
-        <v>984</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D6" t="s">
-        <v>987</v>
-      </c>
-      <c r="E6" t="s">
-        <v>988</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D7" t="s">
-        <v>991</v>
-      </c>
-      <c r="E7" t="s">
-        <v>992</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D8" t="s">
-        <v>995</v>
-      </c>
-      <c r="E8" t="s">
-        <v>996</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D9" t="s">
-        <v>999</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1062</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8602,8 +8859,9 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:G23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr codeName="Tabelle14"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -8612,26 +8870,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8658,383 +8916,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1100</v>
+        <v>976</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1101</v>
+        <v>977</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D4" t="s">
-        <v>1103</v>
+        <v>979</v>
       </c>
       <c r="E4" t="s">
-        <v>1104</v>
+        <v>980</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1105</v>
+        <v>981</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1106</v>
+        <v>982</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D5" t="s">
-        <v>1107</v>
+        <v>983</v>
       </c>
       <c r="E5" t="s">
-        <v>1108</v>
+        <v>984</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1109</v>
+        <v>985</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1110</v>
+        <v>986</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D6" t="s">
-        <v>1111</v>
+        <v>987</v>
       </c>
       <c r="E6" t="s">
-        <v>1112</v>
+        <v>988</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1113</v>
+        <v>989</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1114</v>
+        <v>990</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D7" t="s">
-        <v>1115</v>
+        <v>991</v>
       </c>
       <c r="E7" t="s">
-        <v>1116</v>
+        <v>992</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1117</v>
+        <v>993</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1118</v>
+        <v>994</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D8" t="s">
-        <v>1119</v>
+        <v>995</v>
       </c>
       <c r="E8" t="s">
-        <v>1120</v>
+        <v>996</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1121</v>
+        <v>997</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1122</v>
+        <v>998</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D9" t="s">
-        <v>1123</v>
+        <v>999</v>
       </c>
       <c r="E9" t="s">
-        <v>1124</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1125</v>
+        <v>1001</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1126</v>
+        <v>1002</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D10" t="s">
-        <v>1127</v>
+        <v>1003</v>
       </c>
       <c r="E10" t="s">
-        <v>1128</v>
+        <v>1004</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1129</v>
+        <v>1005</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1130</v>
+        <v>1006</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D11" t="s">
-        <v>1131</v>
+        <v>1007</v>
       </c>
       <c r="E11" t="s">
-        <v>1132</v>
+        <v>1008</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1133</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1134</v>
+        <v>1010</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D12" t="s">
-        <v>1135</v>
+        <v>1011</v>
       </c>
       <c r="E12" t="s">
-        <v>1136</v>
+        <v>1012</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1137</v>
+        <v>1013</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1138</v>
+        <v>1014</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D13" t="s">
-        <v>1139</v>
+        <v>1015</v>
       </c>
       <c r="E13" t="s">
-        <v>1140</v>
+        <v>1016</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1141</v>
+        <v>1017</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1142</v>
+        <v>1018</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D14" t="s">
-        <v>1143</v>
+        <v>1019</v>
       </c>
       <c r="E14" t="s">
-        <v>1144</v>
+        <v>1020</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1145</v>
+        <v>1021</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1146</v>
+        <v>1022</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D15" t="s">
-        <v>1147</v>
+        <v>1023</v>
       </c>
       <c r="E15" t="s">
-        <v>1148</v>
+        <v>1024</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1149</v>
+        <v>1025</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1150</v>
+        <v>1026</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D16" t="s">
-        <v>1151</v>
+        <v>1027</v>
       </c>
       <c r="E16" t="s">
-        <v>1152</v>
+        <v>1028</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1153</v>
+        <v>1029</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1154</v>
+        <v>1030</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D17" t="s">
-        <v>1155</v>
+        <v>1031</v>
       </c>
       <c r="E17" t="s">
-        <v>1156</v>
+        <v>1032</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1157</v>
+        <v>1033</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1158</v>
+        <v>1034</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1102</v>
+        <v>978</v>
       </c>
       <c r="D18" t="s">
-        <v>1159</v>
+        <v>1035</v>
       </c>
       <c r="E18" t="s">
-        <v>1160</v>
+        <v>1036</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1163</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1167</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1175</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9047,8 +9210,9 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:G26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr codeName="Tabelle15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -9057,26 +9221,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9103,364 +9267,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1182</v>
+        <v>1038</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1183</v>
+        <v>1039</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1185</v>
-      </c>
+        <v>1040</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1186</v>
+        <v>1043</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1183</v>
+        <v>1044</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1046</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1187</v>
+        <v>1047</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1188</v>
+        <v>1048</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1050</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1189</v>
+        <v>1051</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1190</v>
+        <v>1052</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1054</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1191</v>
+        <v>1055</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1192</v>
+        <v>1056</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1058</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1193</v>
+        <v>1059</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1194</v>
+        <v>1060</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D9" t="s">
-        <v>1183</v>
+        <v>1061</v>
       </c>
       <c r="E9" t="s">
-        <v>1195</v>
+        <v>1062</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1196</v>
+        <v>1063</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1197</v>
+        <v>1064</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D10" t="s">
-        <v>1198</v>
+        <v>1065</v>
       </c>
       <c r="E10" t="s">
-        <v>1199</v>
+        <v>1066</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1200</v>
+        <v>1067</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1201</v>
+        <v>1068</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D11" t="s">
-        <v>1202</v>
+        <v>1069</v>
       </c>
       <c r="E11" t="s">
-        <v>1203</v>
+        <v>1070</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1204</v>
+        <v>1071</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1205</v>
+        <v>1072</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D12" t="s">
-        <v>1206</v>
+        <v>1073</v>
       </c>
       <c r="E12" t="s">
-        <v>1207</v>
+        <v>1074</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1208</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1209</v>
+        <v>1076</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D13" t="s">
-        <v>1210</v>
+        <v>1077</v>
       </c>
       <c r="E13" t="s">
-        <v>1211</v>
+        <v>1078</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1212</v>
+        <v>1079</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1213</v>
+        <v>1080</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D14" t="s">
-        <v>1214</v>
+        <v>1081</v>
       </c>
       <c r="E14" t="s">
-        <v>1215</v>
+        <v>1082</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1216</v>
+        <v>1083</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1217</v>
+        <v>1084</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D15" t="s">
-        <v>1218</v>
+        <v>1085</v>
       </c>
       <c r="E15" t="s">
-        <v>1219</v>
+        <v>1086</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1220</v>
+        <v>1087</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1221</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D16" t="s">
-        <v>1222</v>
+        <v>1089</v>
       </c>
       <c r="E16" t="s">
-        <v>1223</v>
+        <v>1090</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1224</v>
+        <v>1091</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1225</v>
+        <v>1092</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D17" t="s">
-        <v>1226</v>
+        <v>1093</v>
       </c>
       <c r="E17" t="s">
-        <v>1227</v>
+        <v>1094</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1228</v>
+        <v>1095</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1229</v>
+        <v>1096</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1184</v>
+        <v>1040</v>
       </c>
       <c r="D18" t="s">
-        <v>1230</v>
+        <v>1097</v>
       </c>
       <c r="E18" t="s">
-        <v>1231</v>
+        <v>1098</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1234</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1237</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1238</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1239</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1240</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1242</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>1243</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>1245</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1246</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1248</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>1249</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1250</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1184</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9473,8 +9561,9 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:G18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr codeName="Tabelle16"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -9483,26 +9572,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1252</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9529,288 +9618,383 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1253</v>
+        <v>1100</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1254</v>
+        <v>1101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D4" t="s">
-        <v>1256</v>
+        <v>1103</v>
       </c>
       <c r="E4" t="s">
-        <v>1257</v>
+        <v>1104</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>891</v>
+        <v>1105</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1258</v>
+        <v>1106</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D5" t="s">
-        <v>1259</v>
+        <v>1107</v>
       </c>
       <c r="E5" t="s">
-        <v>1260</v>
+        <v>1108</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1261</v>
+        <v>1109</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1262</v>
+        <v>1110</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D6" t="s">
-        <v>1263</v>
+        <v>1111</v>
       </c>
       <c r="E6" t="s">
-        <v>1264</v>
+        <v>1112</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1265</v>
+        <v>1113</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1266</v>
+        <v>1114</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D7" t="s">
-        <v>1267</v>
+        <v>1115</v>
       </c>
       <c r="E7" t="s">
-        <v>1268</v>
+        <v>1116</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1269</v>
+        <v>1117</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1270</v>
+        <v>1118</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D8" t="s">
-        <v>1271</v>
+        <v>1119</v>
       </c>
       <c r="E8" t="s">
-        <v>1272</v>
+        <v>1120</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1273</v>
+        <v>1121</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1274</v>
+        <v>1122</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D9" t="s">
-        <v>1275</v>
+        <v>1123</v>
       </c>
       <c r="E9" t="s">
-        <v>1276</v>
+        <v>1124</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1277</v>
+        <v>1125</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1278</v>
+        <v>1126</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D10" t="s">
-        <v>1279</v>
+        <v>1127</v>
       </c>
       <c r="E10" t="s">
-        <v>1280</v>
+        <v>1128</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1281</v>
+        <v>1129</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1282</v>
+        <v>1130</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D11" t="s">
-        <v>1283</v>
+        <v>1131</v>
       </c>
       <c r="E11" t="s">
-        <v>1284</v>
+        <v>1132</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1285</v>
+        <v>1133</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1286</v>
+        <v>1134</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D12" t="s">
-        <v>1287</v>
+        <v>1135</v>
       </c>
       <c r="E12" t="s">
-        <v>1288</v>
+        <v>1136</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1289</v>
+        <v>1137</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1290</v>
+        <v>1138</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D13" t="s">
-        <v>1291</v>
+        <v>1139</v>
       </c>
       <c r="E13" t="s">
-        <v>1292</v>
+        <v>1140</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1293</v>
+        <v>1141</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1294</v>
+        <v>1142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D14" t="s">
-        <v>1295</v>
+        <v>1143</v>
       </c>
       <c r="E14" t="s">
-        <v>1296</v>
+        <v>1144</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1297</v>
+        <v>1145</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1298</v>
+        <v>1146</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D15" t="s">
-        <v>1299</v>
+        <v>1147</v>
       </c>
       <c r="E15" t="s">
-        <v>1300</v>
+        <v>1148</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1301</v>
+        <v>1149</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1302</v>
+        <v>1150</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D16" t="s">
-        <v>1303</v>
+        <v>1151</v>
       </c>
       <c r="E16" t="s">
-        <v>1304</v>
+        <v>1152</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1305</v>
+        <v>1153</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1306</v>
+        <v>1154</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D17" t="s">
-        <v>1307</v>
+        <v>1155</v>
       </c>
       <c r="E17" t="s">
-        <v>1308</v>
+        <v>1156</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1309</v>
+        <v>1157</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1310</v>
+        <v>1158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1255</v>
+        <v>1102</v>
       </c>
       <c r="D18" t="s">
-        <v>1311</v>
+        <v>1159</v>
       </c>
       <c r="E18" t="s">
-        <v>1312</v>
+        <v>1160</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9823,8 +10007,9 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr codeName="Tabelle17"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -9833,26 +10018,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9879,288 +10064,364 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1314</v>
+        <v>1182</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1315</v>
+        <v>1183</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>1184</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1185</v>
+      </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1319</v>
+        <v>1186</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1320</v>
+        <v>1183</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1322</v>
+        <v>1184</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1323</v>
+        <v>1187</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1324</v>
+        <v>1188</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1325</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1326</v>
+        <v>1184</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1327</v>
+        <v>1189</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1328</v>
+        <v>1190</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1330</v>
+        <v>1184</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1331</v>
+        <v>1191</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1332</v>
+        <v>1192</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1333</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1334</v>
+        <v>1184</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1335</v>
+        <v>1193</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1336</v>
+        <v>1194</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D9" t="s">
-        <v>1337</v>
+        <v>1183</v>
       </c>
       <c r="E9" t="s">
-        <v>1338</v>
+        <v>1195</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1339</v>
+        <v>1196</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1340</v>
+        <v>1197</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D10" t="s">
-        <v>1341</v>
+        <v>1198</v>
       </c>
       <c r="E10" t="s">
-        <v>1342</v>
+        <v>1199</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1343</v>
+        <v>1200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1344</v>
+        <v>1201</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D11" t="s">
-        <v>1345</v>
+        <v>1202</v>
       </c>
       <c r="E11" t="s">
-        <v>1346</v>
+        <v>1203</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1347</v>
+        <v>1204</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1348</v>
+        <v>1205</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D12" t="s">
-        <v>1349</v>
+        <v>1206</v>
       </c>
       <c r="E12" t="s">
-        <v>1350</v>
+        <v>1207</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1351</v>
+        <v>1208</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1352</v>
+        <v>1209</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D13" t="s">
-        <v>1353</v>
+        <v>1210</v>
       </c>
       <c r="E13" t="s">
-        <v>1354</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1355</v>
+        <v>1212</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1356</v>
+        <v>1213</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D14" t="s">
-        <v>1357</v>
+        <v>1214</v>
       </c>
       <c r="E14" t="s">
-        <v>1358</v>
+        <v>1215</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1359</v>
+        <v>1216</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1360</v>
+        <v>1217</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D15" t="s">
-        <v>1361</v>
+        <v>1218</v>
       </c>
       <c r="E15" t="s">
-        <v>1362</v>
+        <v>1219</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1363</v>
+        <v>1220</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1364</v>
+        <v>1221</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D16" t="s">
-        <v>1365</v>
+        <v>1222</v>
       </c>
       <c r="E16" t="s">
-        <v>1366</v>
+        <v>1223</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1367</v>
+        <v>1224</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1368</v>
+        <v>1225</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D17" t="s">
-        <v>1369</v>
+        <v>1226</v>
       </c>
       <c r="E17" t="s">
-        <v>1370</v>
+        <v>1227</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1371</v>
+        <v>1228</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1372</v>
+        <v>1229</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1316</v>
+        <v>1184</v>
       </c>
       <c r="D18" t="s">
-        <v>1373</v>
+        <v>1230</v>
       </c>
       <c r="E18" t="s">
-        <v>1374</v>
+        <v>1231</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1234</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>1251</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1184</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10174,6 +10435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Tabelle2"/>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -10184,26 +10446,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10902,8 +11164,9 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <sheetPr codeName="Tabelle18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -10912,26 +11175,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1375</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10958,193 +11221,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1376</v>
+        <v>1253</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1377</v>
+        <v>1254</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D4" t="s">
-        <v>1379</v>
+        <v>1256</v>
       </c>
       <c r="E4" t="s">
-        <v>1380</v>
+        <v>1257</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1381</v>
+        <v>891</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1382</v>
+        <v>1258</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D5" t="s">
-        <v>1383</v>
+        <v>1259</v>
       </c>
       <c r="E5" t="s">
-        <v>1384</v>
+        <v>1260</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1385</v>
+        <v>1261</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1386</v>
+        <v>1262</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D6" t="s">
-        <v>1387</v>
+        <v>1263</v>
       </c>
       <c r="E6" t="s">
-        <v>1388</v>
+        <v>1264</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1389</v>
+        <v>1265</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1390</v>
+        <v>1266</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D7" t="s">
-        <v>1391</v>
+        <v>1267</v>
       </c>
       <c r="E7" t="s">
-        <v>1392</v>
+        <v>1268</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1393</v>
+        <v>1269</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1394</v>
+        <v>1270</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D8" t="s">
-        <v>1395</v>
+        <v>1271</v>
       </c>
       <c r="E8" t="s">
-        <v>1396</v>
+        <v>1272</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1397</v>
+        <v>1273</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1398</v>
+        <v>1274</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D9" t="s">
-        <v>1399</v>
+        <v>1275</v>
       </c>
       <c r="E9" t="s">
-        <v>1400</v>
+        <v>1276</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1401</v>
+        <v>1277</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1402</v>
+        <v>1278</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D10" t="s">
-        <v>1403</v>
+        <v>1279</v>
       </c>
       <c r="E10" t="s">
-        <v>1404</v>
+        <v>1280</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1405</v>
+        <v>1281</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1406</v>
+        <v>1282</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D11" t="s">
-        <v>1407</v>
+        <v>1283</v>
       </c>
       <c r="E11" t="s">
-        <v>1408</v>
+        <v>1284</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1409</v>
+        <v>1285</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1410</v>
+        <v>1286</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D12" t="s">
-        <v>1411</v>
+        <v>1287</v>
       </c>
       <c r="E12" t="s">
-        <v>1412</v>
+        <v>1288</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1413</v>
+        <v>1289</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1414</v>
+        <v>1290</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1378</v>
+        <v>1255</v>
       </c>
       <c r="D13" t="s">
-        <v>1415</v>
+        <v>1291</v>
       </c>
       <c r="E13" t="s">
-        <v>1416</v>
+        <v>1292</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11157,8 +11515,9 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:G28"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <sheetPr codeName="Tabelle19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -11167,26 +11526,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1417</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11213,478 +11572,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1418</v>
+        <v>1314</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1419</v>
+        <v>1315</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D4" t="s">
-        <v>1421</v>
+        <v>1317</v>
       </c>
       <c r="E4" t="s">
-        <v>1422</v>
+        <v>1318</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1423</v>
+        <v>1319</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1424</v>
+        <v>1320</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D5" t="s">
-        <v>1425</v>
+        <v>1321</v>
       </c>
       <c r="E5" t="s">
-        <v>1426</v>
+        <v>1322</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1427</v>
+        <v>1323</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1428</v>
+        <v>1324</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D6" t="s">
-        <v>1429</v>
+        <v>1325</v>
       </c>
       <c r="E6" t="s">
-        <v>1430</v>
+        <v>1326</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1431</v>
+        <v>1327</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1432</v>
+        <v>1328</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D7" t="s">
-        <v>1433</v>
+        <v>1329</v>
       </c>
       <c r="E7" t="s">
-        <v>1434</v>
+        <v>1330</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1435</v>
+        <v>1331</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1436</v>
+        <v>1332</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D8" t="s">
-        <v>1437</v>
+        <v>1333</v>
       </c>
       <c r="E8" t="s">
-        <v>1438</v>
+        <v>1334</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1439</v>
+        <v>1335</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1440</v>
+        <v>1336</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D9" t="s">
-        <v>1441</v>
+        <v>1337</v>
       </c>
       <c r="E9" t="s">
-        <v>1442</v>
+        <v>1338</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1443</v>
+        <v>1339</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1444</v>
+        <v>1340</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D10" t="s">
-        <v>1445</v>
+        <v>1341</v>
       </c>
       <c r="E10" t="s">
-        <v>1446</v>
+        <v>1342</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1447</v>
+        <v>1343</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1448</v>
+        <v>1344</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D11" t="s">
-        <v>1449</v>
+        <v>1345</v>
       </c>
       <c r="E11" t="s">
-        <v>1450</v>
+        <v>1346</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1451</v>
+        <v>1347</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1452</v>
+        <v>1348</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D12" t="s">
-        <v>1453</v>
+        <v>1349</v>
       </c>
       <c r="E12" t="s">
-        <v>1454</v>
+        <v>1350</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1455</v>
+        <v>1351</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1456</v>
+        <v>1352</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D13" t="s">
-        <v>1457</v>
+        <v>1353</v>
       </c>
       <c r="E13" t="s">
-        <v>1458</v>
+        <v>1354</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1459</v>
+        <v>1355</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1460</v>
+        <v>1356</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D14" t="s">
-        <v>1461</v>
+        <v>1357</v>
       </c>
       <c r="E14" t="s">
-        <v>1462</v>
+        <v>1358</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1463</v>
+        <v>1359</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1464</v>
+        <v>1360</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D15" t="s">
-        <v>1465</v>
+        <v>1361</v>
       </c>
       <c r="E15" t="s">
-        <v>1466</v>
+        <v>1362</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1467</v>
+        <v>1363</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1468</v>
+        <v>1364</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D16" t="s">
-        <v>1469</v>
+        <v>1365</v>
       </c>
       <c r="E16" t="s">
-        <v>1470</v>
+        <v>1366</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1471</v>
+        <v>1367</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1472</v>
+        <v>1368</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D17" t="s">
-        <v>1473</v>
+        <v>1369</v>
       </c>
       <c r="E17" t="s">
-        <v>1474</v>
+        <v>1370</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1475</v>
+        <v>1371</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1476</v>
+        <v>1372</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1420</v>
+        <v>1316</v>
       </c>
       <c r="D18" t="s">
-        <v>1477</v>
+        <v>1373</v>
       </c>
       <c r="E18" t="s">
-        <v>1478</v>
+        <v>1374</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1118</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1479</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1480</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1483</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1484</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1485</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1486</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1487</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1488</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1489</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1491</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1492</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1494</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1495</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1497</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1499</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1500</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1501</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1503</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1504</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1505</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1506</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1507</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1508</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1510</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1511</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1514</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1515</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1516</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11697,8 +11866,9 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:G18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <sheetPr codeName="Tabelle20"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -11707,26 +11877,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1517</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11753,288 +11923,193 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1518</v>
+        <v>1376</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1519</v>
+        <v>1377</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D4" t="s">
-        <v>1521</v>
+        <v>1379</v>
       </c>
       <c r="E4" t="s">
-        <v>1522</v>
+        <v>1380</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1523</v>
+        <v>1381</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1524</v>
+        <v>1382</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D5" t="s">
-        <v>1525</v>
+        <v>1383</v>
       </c>
       <c r="E5" t="s">
-        <v>1526</v>
+        <v>1384</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1527</v>
+        <v>1385</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1528</v>
+        <v>1386</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D6" t="s">
-        <v>1529</v>
+        <v>1387</v>
       </c>
       <c r="E6" t="s">
-        <v>1530</v>
+        <v>1388</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1531</v>
+        <v>1389</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>492</v>
+        <v>1390</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D7" t="s">
-        <v>1532</v>
+        <v>1391</v>
       </c>
       <c r="E7" t="s">
-        <v>1533</v>
+        <v>1392</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1534</v>
+        <v>1393</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1535</v>
+        <v>1394</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D8" t="s">
-        <v>1536</v>
+        <v>1395</v>
       </c>
       <c r="E8" t="s">
-        <v>1537</v>
+        <v>1396</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1538</v>
+        <v>1397</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1539</v>
+        <v>1398</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D9" t="s">
-        <v>1540</v>
+        <v>1399</v>
       </c>
       <c r="E9" t="s">
-        <v>1541</v>
+        <v>1400</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1542</v>
+        <v>1401</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1543</v>
+        <v>1402</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D10" t="s">
-        <v>1544</v>
+        <v>1403</v>
       </c>
       <c r="E10" t="s">
-        <v>1545</v>
+        <v>1404</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1546</v>
+        <v>1405</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1547</v>
+        <v>1406</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D11" t="s">
-        <v>1548</v>
+        <v>1407</v>
       </c>
       <c r="E11" t="s">
-        <v>1549</v>
+        <v>1408</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1550</v>
+        <v>1409</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1551</v>
+        <v>1410</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D12" t="s">
-        <v>1552</v>
+        <v>1411</v>
       </c>
       <c r="E12" t="s">
-        <v>1553</v>
+        <v>1412</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1554</v>
+        <v>1413</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1555</v>
+        <v>1414</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1520</v>
+        <v>1378</v>
       </c>
       <c r="D13" t="s">
-        <v>1556</v>
+        <v>1415</v>
       </c>
       <c r="E13" t="s">
-        <v>1557</v>
+        <v>1416</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1558</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1559</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1560</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1561</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1562</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1563</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1564</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1568</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1569</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1570</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1571</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1572</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1573</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1576</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1577</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12047,8 +12122,9 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <sheetPr codeName="Tabelle21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -12057,26 +12133,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1578</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12103,136 +12179,478 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1579</v>
+        <v>1418</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1580</v>
+        <v>1419</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D4" t="s">
-        <v>1582</v>
+        <v>1421</v>
       </c>
       <c r="E4" t="s">
-        <v>1583</v>
+        <v>1422</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1584</v>
+        <v>1423</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1585</v>
+        <v>1424</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D5" t="s">
-        <v>1586</v>
+        <v>1425</v>
       </c>
       <c r="E5" t="s">
-        <v>1587</v>
+        <v>1426</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1588</v>
+        <v>1427</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1589</v>
+        <v>1428</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D6" t="s">
-        <v>1590</v>
+        <v>1429</v>
       </c>
       <c r="E6" t="s">
-        <v>1591</v>
+        <v>1430</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1592</v>
+        <v>1431</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1593</v>
+        <v>1432</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D7" t="s">
-        <v>1594</v>
+        <v>1433</v>
       </c>
       <c r="E7" t="s">
-        <v>1595</v>
+        <v>1434</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1596</v>
+        <v>1435</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1597</v>
+        <v>1436</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D8" t="s">
-        <v>1598</v>
+        <v>1437</v>
       </c>
       <c r="E8" t="s">
-        <v>1599</v>
+        <v>1438</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1600</v>
+        <v>1439</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1601</v>
+        <v>1440</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D9" t="s">
-        <v>1602</v>
+        <v>1441</v>
       </c>
       <c r="E9" t="s">
-        <v>1603</v>
+        <v>1442</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1604</v>
+        <v>1443</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1605</v>
+        <v>1444</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1581</v>
+        <v>1420</v>
       </c>
       <c r="D10" t="s">
-        <v>1606</v>
+        <v>1445</v>
       </c>
       <c r="E10" t="s">
-        <v>1607</v>
+        <v>1446</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1488</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1512</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1516</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12245,8 +12663,9 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <sheetPr codeName="Tabelle22"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -12255,26 +12674,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12301,155 +12720,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>1518</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>1519</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>1521</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>1522</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>1523</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>1524</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>1525</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>1526</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>1527</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>1528</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>1529</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>1530</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>1531</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>492</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>1532</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>1533</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>1534</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>1535</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>1536</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>1537</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>1538</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>1539</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>1540</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>1541</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>1542</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>1543</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>1544</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>1545</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>1546</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>1547</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>11</v>
+        <v>1520</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>1548</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>1549</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1556</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1564</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12462,8 +13014,9 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:G18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <sheetPr codeName="Tabelle23"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -12472,26 +13025,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1608</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12518,288 +13071,136 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1609</v>
+        <v>1579</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1610</v>
+        <v>1580</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D4" t="s">
-        <v>1612</v>
+        <v>1582</v>
       </c>
       <c r="E4" t="s">
-        <v>1613</v>
+        <v>1583</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1614</v>
+        <v>1584</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1615</v>
+        <v>1585</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D5" t="s">
-        <v>1616</v>
+        <v>1586</v>
       </c>
       <c r="E5" t="s">
-        <v>1617</v>
+        <v>1587</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1618</v>
+        <v>1588</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1619</v>
+        <v>1589</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D6" t="s">
-        <v>1620</v>
+        <v>1590</v>
       </c>
       <c r="E6" t="s">
-        <v>1621</v>
+        <v>1591</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1622</v>
+        <v>1592</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1623</v>
+        <v>1593</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D7" t="s">
-        <v>1624</v>
+        <v>1594</v>
       </c>
       <c r="E7" t="s">
-        <v>1625</v>
+        <v>1595</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1626</v>
+        <v>1596</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1627</v>
+        <v>1597</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D8" t="s">
-        <v>1628</v>
+        <v>1598</v>
       </c>
       <c r="E8" t="s">
-        <v>1629</v>
+        <v>1599</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1630</v>
+        <v>1600</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1631</v>
+        <v>1601</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D9" t="s">
-        <v>1632</v>
+        <v>1602</v>
       </c>
       <c r="E9" t="s">
-        <v>1633</v>
+        <v>1603</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1634</v>
+        <v>1604</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1635</v>
+        <v>1605</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1611</v>
+        <v>1581</v>
       </c>
       <c r="D10" t="s">
-        <v>1636</v>
+        <v>1606</v>
       </c>
       <c r="E10" t="s">
-        <v>1637</v>
+        <v>1607</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1640</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1651</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1654</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1660</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1664</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1669</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12812,8 +13213,9 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:G15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <sheetPr codeName="Tabelle24"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -12822,26 +13224,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1670</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12868,231 +13270,155 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1671</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1672</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>1674</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>1675</v>
+        <v>13</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1676</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1677</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>1678</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>1679</v>
+        <v>17</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1680</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1681</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>1682</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>1683</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1684</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1685</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>1686</v>
+        <v>23</v>
       </c>
       <c r="E7" t="s">
-        <v>1687</v>
+        <v>24</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1688</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1689</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>1690</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>1691</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1692</v>
+        <v>29</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1693</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>1694</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>1695</v>
+        <v>32</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1696</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1697</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>1698</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>1699</v>
+        <v>36</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1700</v>
+        <v>37</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1701</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1673</v>
+        <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>1702</v>
+        <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>1703</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1704</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1705</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1706</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1707</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1708</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1709</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1710</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1711</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1712</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1713</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1714</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1715</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1716</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1717</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1673</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1718</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1719</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -13105,8 +13431,9 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:G31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <sheetPr codeName="Tabelle25"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -13115,26 +13442,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1720</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13161,367 +13488,288 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1721</v>
+        <v>1609</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1722</v>
+        <v>1610</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1613</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1724</v>
+        <v>1614</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1725</v>
+        <v>1615</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1617</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1726</v>
+        <v>1618</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1727</v>
+        <v>1619</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1621</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1728</v>
+        <v>1622</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1729</v>
+        <v>1623</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1625</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1730</v>
+        <v>1626</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1731</v>
+        <v>1627</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1629</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1732</v>
+        <v>1630</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1733</v>
+        <v>1631</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1633</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1734</v>
+        <v>1634</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1735</v>
+        <v>1635</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1637</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1736</v>
+        <v>1638</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1737</v>
+        <v>1639</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1641</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1738</v>
+        <v>1642</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1739</v>
+        <v>1643</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1645</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1740</v>
+        <v>1646</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1741</v>
+        <v>1647</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1649</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1742</v>
+        <v>1650</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1743</v>
+        <v>1651</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1653</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1744</v>
+        <v>1654</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1745</v>
+        <v>1655</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1657</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1746</v>
+        <v>1658</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1747</v>
+        <v>1659</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1661</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1748</v>
+        <v>1662</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1749</v>
+        <v>1663</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1665</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1750</v>
+        <v>1666</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1751</v>
+        <v>1667</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1723</v>
+        <v>1611</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1669</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>1752</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>1753</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>1754</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>1755</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>1756</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>1757</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>1758</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>1760</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1761</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>1763</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>1764</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>1765</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>1766</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>1767</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>1768</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>1769</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>1770</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>1771</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>1772</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>1773</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>1774</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>1775</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>1777</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -13534,8 +13782,9 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
-  <dimension ref="A1:G42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+  <sheetPr codeName="Tabelle26"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -13544,26 +13793,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>1780</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="A1" s="13" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13590,500 +13839,675 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>1781</v>
+        <v>1671</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>1782</v>
+        <v>1672</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1675</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>1784</v>
+        <v>1676</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1785</v>
+        <v>1677</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1679</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1786</v>
+        <v>1680</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1787</v>
+        <v>1681</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1683</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1788</v>
+        <v>1684</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1789</v>
+        <v>1685</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1687</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1790</v>
+        <v>1688</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1791</v>
+        <v>1689</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1690</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1691</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1792</v>
+        <v>1692</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1793</v>
+        <v>1693</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1694</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1695</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1794</v>
+        <v>1696</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1795</v>
+        <v>1697</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1699</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1796</v>
+        <v>1700</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1797</v>
+        <v>1701</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1703</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1798</v>
+        <v>1704</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1799</v>
+        <v>1705</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1707</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1800</v>
+        <v>1708</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1801</v>
+        <v>1709</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1711</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1802</v>
+        <v>1712</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1803</v>
+        <v>1713</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1714</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1715</v>
       </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1804</v>
+        <v>1716</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1805</v>
+        <v>1717</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>1783</v>
+        <v>1673</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1719</v>
       </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+  <sheetPr codeName="Tabelle27"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1806</v>
+        <v>1746</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1807</v>
+        <v>1747</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1808</v>
+        <v>1748</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1809</v>
+        <v>1749</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1810</v>
+        <v>1750</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1811</v>
+        <v>1751</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1812</v>
+        <v>1752</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1813</v>
+        <v>1753</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1814</v>
+        <v>1754</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1815</v>
+        <v>1755</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1816</v>
+        <v>1756</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1817</v>
+        <v>1757</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>1818</v>
+        <v>1758</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1819</v>
+        <v>1759</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>1820</v>
+        <v>1760</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1821</v>
+        <v>1761</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>1822</v>
+        <v>1762</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1823</v>
+        <v>1763</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>1824</v>
+        <v>1764</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>1825</v>
+        <v>1765</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>1826</v>
+        <v>1766</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1827</v>
+        <v>1767</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>1828</v>
+        <v>1768</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>1829</v>
+        <v>1769</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>1830</v>
+        <v>1770</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>1831</v>
+        <v>1771</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>1832</v>
+        <v>1772</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1833</v>
+        <v>1773</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>1834</v>
+        <v>1774</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1835</v>
+        <v>1775</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1836</v>
+        <v>1776</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1837</v>
+        <v>1777</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>1783</v>
+        <v>1723</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1839</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1841</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1847</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>1848</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1849</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1853</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>1856</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1859</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1783</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Tabelle3"/>
   <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14487,8 +14911,559 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
+  <sheetPr codeName="Tabelle28"/>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1783</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14502,26 +15477,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14679,6 +15654,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -14690,26 +15666,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15088,6 +16064,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15098,26 +16075,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15528,6 +16505,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -15537,26 +16515,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16030,6 +17008,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Tabelle8"/>
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16040,26 +17019,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16666,6 +17645,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr codeName="Tabelle9"/>
   <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -16675,26 +17655,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">

--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C203CF79-F9F2-48D9-8013-15436C6614E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F60A21-4A9B-4645-A062-9E24A2C730D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2785" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="1995">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -6077,13 +6077,53 @@
   </si>
   <si>
     <t>zwischen</t>
+  </si>
+  <si>
+    <t>dritto</t>
+  </si>
+  <si>
+    <t>gerade, geradeaus, gerade</t>
+  </si>
+  <si>
+    <t>girare</t>
+  </si>
+  <si>
+    <t>abbiegen</t>
+  </si>
+  <si>
+    <t>zurückkehren, zurückkommen</t>
+  </si>
+  <si>
+    <t>indietro</t>
+  </si>
+  <si>
+    <t>zurück, rückwärts, nach hinten</t>
+  </si>
+  <si>
+    <t>überqueren, durchqueren</t>
+  </si>
+  <si>
+    <t>die Querstraße, die Seitenstraße</t>
+  </si>
+  <si>
+    <t>überholen, überschreiten, 
+bewältigen, bestehen</t>
+  </si>
+  <si>
+    <t>attraversare</t>
+  </si>
+  <si>
+    <t>la traversa</t>
+  </si>
+  <si>
+    <t>superare</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6147,6 +6187,17 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6175,7 +6226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6198,11 +6249,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -6544,23 +6597,23 @@
       <c r="A1" s="13" t="s">
         <v>735</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>736</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -6973,23 +7026,23 @@
       <c r="A1" s="13" t="s">
         <v>813</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7361,23 +7414,23 @@
       <c r="A1" s="13" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7589,23 +7642,23 @@
       <c r="A1" s="13" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7835,7 +7888,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0357D6F-E5C9-4C7A-8B99-03AFE50AD46D}">
   <sheetPr codeName="Tabelle29"/>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -7854,15 +7907,15 @@
       <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7971,7 +8024,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="20" t="s">
         <v>1902</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -8211,6 +8264,97 @@
       <c r="C32" s="2" t="s">
         <v>1889</v>
       </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C41" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8237,23 +8381,23 @@
       <c r="A1" s="13" t="s">
         <v>852</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8873,23 +9017,23 @@
       <c r="A1" s="13" t="s">
         <v>975</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9224,23 +9368,23 @@
       <c r="A1" s="13" t="s">
         <v>1037</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9575,23 +9719,23 @@
       <c r="A1" s="13" t="s">
         <v>1099</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10021,23 +10165,23 @@
       <c r="A1" s="13" t="s">
         <v>1181</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10449,23 +10593,23 @@
       <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11178,23 +11322,23 @@
       <c r="A1" s="13" t="s">
         <v>1252</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11529,23 +11673,23 @@
       <c r="A1" s="13" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11880,23 +12024,23 @@
       <c r="A1" s="13" t="s">
         <v>1375</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12136,23 +12280,23 @@
       <c r="A1" s="13" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12677,23 +12821,23 @@
       <c r="A1" s="13" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13028,23 +13172,23 @@
       <c r="A1" s="13" t="s">
         <v>1578</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13227,23 +13371,23 @@
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13445,23 +13589,23 @@
       <c r="A1" s="13" t="s">
         <v>1608</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13796,23 +13940,23 @@
       <c r="A1" s="13" t="s">
         <v>1670</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14090,23 +14234,23 @@
       <c r="A1" s="13" t="s">
         <v>1720</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14926,23 +15070,23 @@
       <c r="A1" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15480,23 +15624,23 @@
       <c r="A1" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15669,23 +15813,23 @@
       <c r="A1" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16078,23 +16222,23 @@
       <c r="A1" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16518,23 +16662,23 @@
       <c r="A1" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -17022,23 +17166,23 @@
       <c r="A1" s="13" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -17658,23 +17802,23 @@
       <c r="A1" s="13" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
